--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -418,13 +418,13 @@
         <v>版本A</v>
       </c>
       <c r="B2" t="str">
-        <v>夏天不戴口罩，你的脸会变成什么样？</v>
+        <v>你还在戴那种又闷又热、一蹭就花妆的口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>看看这张对比图，左边是长期不防晒的脸，晒黑、长斑、加速老化，右边是戴了我们3D凉感口罩的脸，白皙透亮。普通口罩又闷又蹭妆，让你在高温下痛苦不堪，还挡不住紫外线伤害。我们的口罩采用UPF500+防晒科技，紫外线灯测试完全透不过，立体空间设计不贴脸，呼吸顺畅不闷热，凉感网纱触感冰凉，全天舒适不勒耳。别再让晒黑和冻伤毁掉你的夏天，赶紧行动！</v>
+        <v>夏天不换口罩，等着晒成阴阳脸、闷出一脸痘吗？普通口罩防晒力不够，紫外线穿透，皮肤老化、长斑你怕不怕？冻伤？不存在的，但晒黑是实打实的！我这款3D凉感口罩，UPF500+，紫外线灯都照不透。3D立体设计不贴脸，呼吸顺畅不闷痘。凉感网纱冰冰凉，口红不蹭，干净卫生。再戴旧口罩，等着后悔吧！</v>
       </c>
       <c r="D2" t="str">
-        <v>点击下方链接，立即抢购这款防晒神器，保护你的肌肤，告别晒伤烦恼！</v>
+        <v>别拿脸开玩笑，现在下单，买二送一，赶紧上车！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>早上化好全妆，出门一戴口罩全花了？</v>
+        <v>通勤路上、户外逛街，你还在忍受口罩的闷热花妆？</v>
       </c>
       <c r="C3" t="str">
-        <v>想象一下，你精心打扮准备约会，戴上普通口罩，口红蹭花、妆容全毁，尴尬又浪费时间。现在换上我们的3D凉感口罩，立体空间设计让口鼻不贴脸，呼吸自由不闷热，关键是不蹭妆，里面干干净净。UPF500+防晒力，紫外线灯测试光线透不过，夏天出门逛街、通勤都安全感满满。凉感网纱触感冰凉，戴一整天也不勒耳朵，多个颜色百搭时尚。让每一天都清爽自信，不再为花妆烦恼。</v>
+        <v>早上化了一小时精致全妆，出门挤地铁，口罩一戴全蹭花了，补妆补到崩溃。闺蜜推荐我这款3D凉感口罩，3D立体空间不贴嘴，呼吸顺畅不闷热，口红蹭不上去！UPF500+防晒，紫外线全挡，凉感网纱冰冰凉，一整天不勒耳。颜色百搭，搭配衣服也好看。戴上它，夏天出门幸福感爆棚！</v>
       </c>
       <c r="D3" t="str">
-        <v>马上点击购买，体验这款不蹭妆、超透气的口罩，让你的夏日生活更轻松！</v>
+        <v>39.9元5只，一整个夏天够用，点击下方链接，告别闷热花妆！</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>算笔账：防晒霜一年花多少钱？</v>
+        <v>算笔账，防晒霜+医美vs口罩，哪个更划算？</v>
       </c>
       <c r="C4" t="str">
-        <v>一瓶防晒霜几百块，一个月就用完，一年下来几千块，还不算补涂的麻烦和蹭妆的损失。医美修复晒伤更贵，动辄上万。我们的3D凉感口罩，一次购买几十元，UPF500+防晒力媲美专业防晒，立体设计不闷不蹭妆，凉感网纱舒适耐用。对比一下，防晒霜成本高、效果有限，口罩性价比极致，一劳永逸保护肌肤。别再浪费钱在无效防晒上，聪明选择省钱又高效。</v>
+        <v>一瓶防晒霜两三百，还油腻闷痘；一次医美光子嫩肤上千块，还得按时做。而我这款3D凉感口罩，一杯奶茶钱，UPF500+防晒力，紫外线全挡住，还凉感透气不闷痘。3D立体不蹭口红，省下补妆时间。一天不到一块钱，全年防晒到位。性价比之王，算算能省多少钱？</v>
       </c>
       <c r="D4" t="str">
-        <v>立即下单，用这款高性价比口罩替代昂贵防晒，省钱又省心，夏天防晒就靠它！</v>
+        <v>聪明人都会算，现在购买还有限时优惠，点击下方，立刻省下几百块！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -418,13 +418,13 @@
         <v>版本A</v>
       </c>
       <c r="B2" t="str">
-        <v>你还在戴那种又闷又热、一蹭就花妆的口罩？</v>
+        <v>不戴口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>夏天不换口罩，等着晒成阴阳脸、闷出一脸痘吗？普通口罩防晒力不够，紫外线穿透，皮肤老化、长斑你怕不怕？冻伤？不存在的，但晒黑是实打实的！我这款3D凉感口罩，UPF500+，紫外线灯都照不透。3D立体设计不贴脸，呼吸顺畅不闷痘。凉感网纱冰冰凉，口红不蹭，干净卫生。再戴旧口罩，等着后悔吧！</v>
+        <v>紫外线照10分钟，皮肤晒黑长斑，光老化加速，比同龄人老10岁！</v>
       </c>
       <c r="D2" t="str">
-        <v>别拿脸开玩笑，现在下单，买二送一，赶紧上车！</v>
+        <v>赶紧戴上！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>通勤路上、户外逛街，你还在忍受口罩的闷热花妆？</v>
+        <v>出门前化妆？</v>
       </c>
       <c r="C3" t="str">
-        <v>早上化了一小时精致全妆，出门挤地铁，口罩一戴全蹭花了，补妆补到崩溃。闺蜜推荐我这款3D凉感口罩，3D立体空间不贴嘴，呼吸顺畅不闷热，口红蹭不上去！UPF500+防晒，紫外线全挡，凉感网纱冰冰凉，一整天不勒耳。颜色百搭，搭配衣服也好看。戴上它，夏天出门幸福感爆棚！</v>
+        <v>刚涂好口红，一戴口罩全蹭花，补妆浪费时间，不如换这个3D凉感口罩！</v>
       </c>
       <c r="D3" t="str">
-        <v>39.9元5只，一整个夏天够用，点击下方链接，告别闷热花妆！</v>
+        <v>试试这个！</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>算笔账，防晒霜+医美vs口罩，哪个更划算？</v>
+        <v>算笔账吧！</v>
       </c>
       <c r="C4" t="str">
-        <v>一瓶防晒霜两三百，还油腻闷痘；一次医美光子嫩肤上千块，还得按时做。而我这款3D凉感口罩，一杯奶茶钱，UPF500+防晒力，紫外线全挡住，还凉感透气不闷痘。3D立体不蹭口红，省下补妆时间。一天不到一块钱，全年防晒到位。性价比之王，算算能省多少钱？</v>
+        <v>防晒霜一月花500，医美一次上千，这个口罩才几十，防晒够用整个夏天！</v>
       </c>
       <c r="D4" t="str">
-        <v>聪明人都会算，现在购买还有限时优惠，点击下方，立刻省下几百块！</v>
+        <v>太划算了！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -418,13 +418,13 @@
         <v>版本A</v>
       </c>
       <c r="B2" t="str">
-        <v>不戴口罩？</v>
+        <v>小心晒出斑！</v>
       </c>
       <c r="C2" t="str">
-        <v>紫外线照10分钟，皮肤晒黑长斑，光老化加速，比同龄人老10岁！</v>
+        <v>不戴口罩，紫外线直射脸，皱纹斑点全找上门。</v>
       </c>
       <c r="D2" t="str">
-        <v>赶紧戴上！</v>
+        <v>赶紧换这款！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>出门前化妆？</v>
+        <v>出门化妆了吗？</v>
       </c>
       <c r="C3" t="str">
-        <v>刚涂好口红，一戴口罩全蹭花，补妆浪费时间，不如换这个3D凉感口罩！</v>
+        <v>刚化好妆一戴口罩全花了，尴尬又浪费。</v>
       </c>
       <c r="D3" t="str">
-        <v>试试这个！</v>
+        <v>试试不蹭妆的！</v>
       </c>
     </row>
     <row r="4">
@@ -449,10 +449,10 @@
         <v>算笔账吧！</v>
       </c>
       <c r="C4" t="str">
-        <v>防晒霜一月花500，医美一次上千，这个口罩才几十，防晒够用整个夏天！</v>
+        <v>一瓶防晒霜几百块，不如这款口罩天天用。</v>
       </c>
       <c r="D4" t="str">
-        <v>太划算了！</v>
+        <v>省钱又省心！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -418,13 +418,13 @@
         <v>版本A</v>
       </c>
       <c r="B2" t="str">
-        <v>小心晒出斑！</v>
+        <v>不戴口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>不戴口罩，紫外线直射脸，皱纹斑点全找上门。</v>
+        <v>晒黑长斑，医美都救不了！</v>
       </c>
       <c r="D2" t="str">
-        <v>赶紧换这款！</v>
+        <v>快戴它！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>出门化妆了吗？</v>
+        <v>通勤路上，</v>
       </c>
       <c r="C3" t="str">
-        <v>刚化好妆一戴口罩全花了，尴尬又浪费。</v>
+        <v>妆花一脸，闷到想哭？</v>
       </c>
       <c r="D3" t="str">
-        <v>试试不蹭妆的！</v>
+        <v>它全解决！</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>算笔账吧！</v>
+        <v>防晒霜一年，</v>
       </c>
       <c r="C4" t="str">
-        <v>一瓶防晒霜几百块，不如这款口罩天天用。</v>
+        <v>够买它十年！</v>
       </c>
       <c r="D4" t="str">
-        <v>省钱又省心！</v>
+        <v>省大钱！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -418,13 +418,13 @@
         <v>版本A</v>
       </c>
       <c r="B2" t="str">
-        <v>不戴口罩？</v>
+        <v>夏天戴口罩闷到烂脸？</v>
       </c>
       <c r="C2" t="str">
-        <v>晒黑长斑，医美都救不了！</v>
+        <v>不戴它，紫外线直射加速衰老，妆花成鬼。</v>
       </c>
       <c r="D2" t="str">
-        <v>快戴它！</v>
+        <v>赶紧换3D凉感口罩！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>通勤路上，</v>
+        <v>刚化完妆出门？</v>
       </c>
       <c r="C3" t="str">
-        <v>妆花一脸，闷到想哭？</v>
+        <v>一戴口罩全蹭花，补妆烦到炸。</v>
       </c>
       <c r="D3" t="str">
-        <v>它全解决！</v>
+        <v>试试这款不蹭妆的凉感口罩！</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>防晒霜一年，</v>
+        <v>防晒霜一年花上千？</v>
       </c>
       <c r="C4" t="str">
-        <v>够买它十年！</v>
+        <v>医美更贵，不如UPF500+口罩，几十块搞定防晒和妆效。</v>
       </c>
       <c r="D4" t="str">
-        <v>省大钱！</v>
+        <v>点击下单，省大钱！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -418,13 +418,13 @@
         <v>版本A</v>
       </c>
       <c r="B2" t="str">
-        <v>夏天戴口罩闷到烂脸？</v>
+        <v>不戴防晒口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>不戴它，紫外线直射加速衰老，妆花成鬼。</v>
+        <v>紫外线晒伤皮肤，长斑皱纹找上门！</v>
       </c>
       <c r="D2" t="str">
-        <v>赶紧换3D凉感口罩！</v>
+        <v>赶紧带上凉感口罩！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>刚化完妆出门？</v>
+        <v>夏天出门化妆</v>
       </c>
       <c r="C3" t="str">
-        <v>一戴口罩全蹭花，补妆烦到炸。</v>
+        <v>口罩蹭花口红，又闷又热！换成3D凉感款，清爽不脱妆。</v>
       </c>
       <c r="D3" t="str">
-        <v>试试这款不蹭妆的凉感口罩！</v>
+        <v>试试它吧！</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>防晒霜一年花上千？</v>
+        <v>防晒霜一年上千</v>
       </c>
       <c r="C4" t="str">
-        <v>医美更贵，不如UPF500+口罩，几十块搞定防晒和妆效。</v>
+        <v>医美更贵！一只口罩搞定防晒，省下大笔钱。</v>
       </c>
       <c r="D4" t="str">
-        <v>点击下单，省大钱！</v>
+        <v>现在下单！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -418,13 +418,13 @@
         <v>版本A</v>
       </c>
       <c r="B2" t="str">
-        <v>不戴防晒口罩？</v>
+        <v>不戴口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>紫外线晒伤皮肤，长斑皱纹找上门！</v>
+        <v>紫外线让你老10岁，晒斑找上门！</v>
       </c>
       <c r="D2" t="str">
-        <v>赶紧带上凉感口罩！</v>
+        <v>这款3D凉感口罩，防蹭还防晒！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>夏天出门化妆</v>
+        <v>出门化妆了吗？</v>
       </c>
       <c r="C3" t="str">
-        <v>口罩蹭花口红，又闷又热！换成3D凉感款，清爽不脱妆。</v>
+        <v>口罩一戴妆全花，口红蹭得脏兮兮！</v>
       </c>
       <c r="D3" t="str">
-        <v>试试它吧！</v>
+        <v>换它，立体不贴脸，干净又透气！</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>防晒霜一年上千</v>
+        <v>防晒霜一瓶几百？</v>
       </c>
       <c r="C4" t="str">
-        <v>医美更贵！一只口罩搞定防晒，省下大笔钱。</v>
+        <v>医美一次上千？不如买个口罩！</v>
       </c>
       <c r="D4" t="str">
-        <v>现在下单！</v>
+        <v>UPF500+凉感网纱，一次到位！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -421,10 +421,10 @@
         <v>不戴口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>紫外线让你老10岁，晒斑找上门！</v>
+        <v>紫外线直射加速衰老，斑点皱纹找上门！</v>
       </c>
       <c r="D2" t="str">
-        <v>这款3D凉感口罩，防蹭还防晒！</v>
+        <v>赶紧戴上！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>出门化妆了吗？</v>
+        <v>早上化妆，</v>
       </c>
       <c r="C3" t="str">
-        <v>口罩一戴妆全花，口红蹭得脏兮兮！</v>
+        <v>出门戴口罩全蹭花？换3D凉感口罩，不闷不蹭，清凉一夏！</v>
       </c>
       <c r="D3" t="str">
-        <v>换它，立体不贴脸，干净又透气！</v>
+        <v>快买它！</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>防晒霜一瓶几百？</v>
+        <v>一瓶防晒霜上百，</v>
       </c>
       <c r="C4" t="str">
-        <v>医美一次上千？不如买个口罩！</v>
+        <v>一次医美上千？这个口罩才几十块，UPF500+，省钱又省心！</v>
       </c>
       <c r="D4" t="str">
-        <v>UPF500+凉感网纱，一次到位！</v>
+        <v>现在下单！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -421,10 +421,10 @@
         <v>不戴口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>紫外线直射加速衰老，斑点皱纹找上门！</v>
+        <v>紫外线直射加速光老化，晒斑皱纹全找上门！</v>
       </c>
       <c r="D2" t="str">
-        <v>赶紧戴上！</v>
+        <v>赶紧戴这款！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>早上化妆，</v>
+        <v>出门戴口罩，</v>
       </c>
       <c r="C3" t="str">
-        <v>出门戴口罩全蹭花？换3D凉感口罩，不闷不蹭，清凉一夏！</v>
+        <v>口红蹭花、闷痘脱妆，补妆烦到崩溃！</v>
       </c>
       <c r="D3" t="str">
-        <v>快买它！</v>
+        <v>换这款不蹭妆！</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>一瓶防晒霜上百，</v>
+        <v>防晒霜一瓶几百，</v>
       </c>
       <c r="C4" t="str">
-        <v>一次医美上千？这个口罩才几十块，UPF500+，省钱又省心！</v>
+        <v>医美一次上千！</v>
       </c>
       <c r="D4" t="str">
-        <v>现在下单！</v>
+        <v>不如这款口罩划算！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -421,10 +421,10 @@
         <v>不戴口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>紫外线直射加速光老化，晒斑皱纹全找上门！</v>
+        <v>紫外线直射皮肤，加速老化！</v>
       </c>
       <c r="D2" t="str">
-        <v>赶紧戴这款！</v>
+        <v>赶紧试试这款！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>出门戴口罩，</v>
+        <v>出门化妆？</v>
       </c>
       <c r="C3" t="str">
-        <v>口红蹭花、闷痘脱妆，补妆烦到崩溃！</v>
+        <v>戴口罩花妆又闷痘，不如换3D凉感款！</v>
       </c>
       <c r="D3" t="str">
-        <v>换这款不蹭妆！</v>
+        <v>买它！</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>防晒霜一瓶几百，</v>
+        <v>防晒霜贵？</v>
       </c>
       <c r="C4" t="str">
-        <v>医美一次上千！</v>
+        <v>一瓶几百，不如口罩UPF500+防晒！</v>
       </c>
       <c r="D4" t="str">
-        <v>不如这款口罩划算！</v>
+        <v>省下医美钱！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -421,10 +421,10 @@
         <v>不戴口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>紫外线直射皮肤，加速老化！</v>
+        <v>紫外线直接晒黑皮肤，衰老快10倍！</v>
       </c>
       <c r="D2" t="str">
-        <v>赶紧试试这款！</v>
+        <v>赶紧戴这个！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>出门化妆？</v>
+        <v>出门前化妆？</v>
       </c>
       <c r="C3" t="str">
-        <v>戴口罩花妆又闷痘，不如换3D凉感款！</v>
+        <v>一戴口罩全蹭花，补妆烦死你！</v>
       </c>
       <c r="D3" t="str">
-        <v>买它！</v>
+        <v>换这个不蹭妆！</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>防晒霜贵？</v>
+        <v>一盒防晒霜几百？</v>
       </c>
       <c r="C4" t="str">
-        <v>一瓶几百，不如口罩UPF500+防晒！</v>
+        <v>医美更贵！这个口罩才几十块，防晒UPF500+！</v>
       </c>
       <c r="D4" t="str">
-        <v>省下医美钱！</v>
+        <v>省钱又省心！</v>
       </c>
     </row>
   </sheetData>

--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,10 +407,16 @@
         <v>hook</v>
       </c>
       <c r="C1" t="str">
-        <v>content</v>
+        <v>pain</v>
       </c>
       <c r="D1" t="str">
-        <v>callToAction</v>
+        <v>proof</v>
+      </c>
+      <c r="E1" t="str">
+        <v>benefit</v>
+      </c>
+      <c r="F1" t="str">
+        <v>cta</v>
       </c>
     </row>
     <row r="2">
@@ -418,13 +424,19 @@
         <v>版本A</v>
       </c>
       <c r="B2" t="str">
-        <v>不戴口罩？</v>
+        <v>你是不是也买过一蹭就花妆、闷到透不过气的夏天口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>紫外线直接晒黑皮肤，衰老快10倍！</v>
+        <v>出门刚戴上，口红蹭一脸，全妆直接废，耳朵勒得生疼，出汗还糊成一片！</v>
       </c>
       <c r="D2" t="str">
-        <v>赶紧戴这个！</v>
+        <v>直接看，涂了口红在里面使劲蹭，一点痕迹都没有！紫外线灯贴着照，光都透不过来！</v>
+      </c>
+      <c r="E2" t="str">
+        <v>戴上它，呼吸顺畅得像没戴，冰冰凉凉一整天，摘下来底妆干干净净，通勤爽到飞起。</v>
+      </c>
+      <c r="F2" t="str">
+        <v>商场杂牌都要几十块，今天一杯奶茶钱带走三条！不好用直接退，赶紧抢！</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +444,19 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>出门前化妆？</v>
+        <v>夏天戴口罩，你是不是也踩过这种雷？</v>
       </c>
       <c r="C3" t="str">
-        <v>一戴口罩全蹭花，补妆烦死你！</v>
+        <v>一戴就闷痘、花妆，口红蹭得到处都是，耳朵勒出红印子，简直是在受刑！</v>
       </c>
       <c r="D3" t="str">
-        <v>换这个不蹭妆！</v>
+        <v>看我用紫外线灯暴力测试，UPF500+防晒，光都透不过！再涂上口红用力蹭，里面干干净净！</v>
+      </c>
+      <c r="E3" t="str">
+        <v>戴上它，口鼻完全不贴脸，呼吸超顺畅，凉感网纱冰冰凉，耳朵跟没挂东西一样。</v>
+      </c>
+      <c r="F3" t="str">
+        <v>别花冤枉钱了！今天一杯奶茶钱三条，零风险承诺，不好用直接退，赶紧下单！</v>
       </c>
     </row>
     <row r="4">
@@ -446,18 +464,24 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>一盒防晒霜几百？</v>
+        <v>你还在用那种一戴就蹭花妆、闷到怀疑人生的口罩吗？</v>
       </c>
       <c r="C4" t="str">
-        <v>医美更贵！这个口罩才几十块，防晒UPF500+！</v>
+        <v>刚化好妆出门，口红糊一脸，全妆白费，耳朵勒得疼，一出汗还黏在脸上！</v>
       </c>
       <c r="D4" t="str">
-        <v>省钱又省心！</v>
+        <v>直接暴力测试！涂口红用力蹭，一点不沾！紫外线灯贴着照，光都透不进去！3D立体空间呼吸超顺！</v>
+      </c>
+      <c r="E4" t="str">
+        <v>戴上它，冰冰凉凉一整天，摘下来底妆完好无损，通勤外出清爽到不想换。</v>
+      </c>
+      <c r="F4" t="str">
+        <v>杂牌一个几十块，今天一杯奶茶钱拿三条！不好用直接退，库存不多，手慢无！</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/generated_scripts.xlsx
+++ b/generated_scripts.xlsx
@@ -424,19 +424,19 @@
         <v>版本A</v>
       </c>
       <c r="B2" t="str">
-        <v>你是不是也买过一蹭就花妆、闷到透不过气的夏天口罩？</v>
+        <v>你是不是也买过那种一戴全妆花成鬼的口罩？</v>
       </c>
       <c r="C2" t="str">
-        <v>出门刚戴上，口红蹭一脸，全妆直接废，耳朵勒得生疼，出汗还糊成一片！</v>
+        <v>夏天出门刚化好妆，一戴口罩全蹭糊了，补妆补到崩溃！</v>
       </c>
       <c r="D2" t="str">
-        <v>直接看，涂了口红在里面使劲蹭，一点痕迹都没有！紫外线灯贴着照，光都透不过来！</v>
+        <v>看我直接涂口红戴上，摘下来里面干干净净，UPF500+紫外线灯照不透！</v>
       </c>
       <c r="E2" t="str">
-        <v>戴上它，呼吸顺畅得像没戴，冰冰凉凉一整天，摘下来底妆干干净净，通勤爽到飞起。</v>
+        <v>3D立体空间不贴脸，呼吸超顺畅，凉感网纱冰冰凉，耳朵不勒一整天！</v>
       </c>
       <c r="F2" t="str">
-        <v>商场杂牌都要几十块，今天一杯奶茶钱带走三条！不好用直接退，赶紧抢！</v>
+        <v>去商场杂牌几十块，今天一杯奶茶钱带走三条，不好用直接退！</v>
       </c>
     </row>
     <row r="3">
@@ -444,19 +444,19 @@
         <v>版本B</v>
       </c>
       <c r="B3" t="str">
-        <v>夏天戴口罩，你是不是也踩过这种雷？</v>
+        <v>谁还戴那种一闷一脸汗的废纸口罩？</v>
       </c>
       <c r="C3" t="str">
-        <v>一戴就闷痘、花妆，口红蹭得到处都是，耳朵勒出红印子，简直是在受刑！</v>
+        <v>夏天一出汗口罩糊脸上，全妆直接毁容，耳朵勒得生疼！</v>
       </c>
       <c r="D3" t="str">
-        <v>看我用紫外线灯暴力测试，UPF500+防晒，光都透不过！再涂上口红用力蹭，里面干干净净！</v>
+        <v>直接拿紫外线灯贴着照，光线透不过一丝，水桶拉扯弹力大到离谱！</v>
       </c>
       <c r="E3" t="str">
-        <v>戴上它，口鼻完全不贴脸，呼吸超顺畅，凉感网纱冰冰凉，耳朵跟没挂东西一样。</v>
+        <v>戴上它口鼻不贴脸，呼吸像没戴，摘下来底妆干干净净，清爽到起飞！</v>
       </c>
       <c r="F3" t="str">
-        <v>别花冤枉钱了！今天一杯奶茶钱三条，零风险承诺，不好用直接退，赶紧下单！</v>
+        <v>杂牌几十块，今天一杯奶茶钱带走三条，零风险退货！</v>
       </c>
     </row>
     <row r="4">
@@ -464,19 +464,19 @@
         <v>版本C</v>
       </c>
       <c r="B4" t="str">
-        <v>你还在用那种一戴就蹭花妆、闷到怀疑人生的口罩吗？</v>
+        <v>你是不是也遇到过口罩蹭花口红？</v>
       </c>
       <c r="C4" t="str">
-        <v>刚化好妆出门，口红糊一脸，全妆白费，耳朵勒得疼，一出汗还黏在脸上！</v>
+        <v>夏天出门戴口罩，刚涂的口红全蹭掉，补妆补到没脾气！</v>
       </c>
       <c r="D4" t="str">
-        <v>直接暴力测试！涂口红用力蹭，一点不沾！紫外线灯贴着照，光都透不进去！3D立体空间呼吸超顺！</v>
+        <v>看我涂口红戴上，摘下来里面一尘不染，UPF500+紫外线灯都透不过！</v>
       </c>
       <c r="E4" t="str">
-        <v>戴上它，冰冰凉凉一整天，摘下来底妆完好无损，通勤外出清爽到不想换。</v>
+        <v>3D立体空间不贴脸，呼吸超顺畅，凉感网纱冰冰凉，耳朵挂一天不勒！</v>
       </c>
       <c r="F4" t="str">
-        <v>杂牌一个几十块，今天一杯奶茶钱拿三条！不好用直接退，库存不多，手慢无！</v>
+        <v>商场杂牌几十块，今天一杯奶茶钱带走三条，不好用直接退！</v>
       </c>
     </row>
   </sheetData>
